--- a/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
@@ -520,9 +520,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -961,7 +967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643ADB76-5C53-4646-851D-C5DA69EBB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E169AD9E-409A-41AE-A8B5-49FB0823B9A7}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
@@ -487,25 +487,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -586,11 +572,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -967,7 +953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E169AD9E-409A-41AE-A8B5-49FB0823B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A60DE78-5D86-46CD-9E87-3DD67D3EBAA6}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A60DE78-5D86-46CD-9E87-3DD67D3EBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D788AB-90F0-4DFA-AE0C-DD49D0E5BAA6}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench PRICE.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D788AB-90F0-4DFA-AE0C-DD49D0E5BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413CC41-D7FC-47DC-BF18-51CB4083BAA6}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
